--- a/static/uploads/mau/hopdong/nt1/duoi_o2/hdtv.xlsx
+++ b/static/uploads/mau/hopdong/nt1/duoi_o2/hdtv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAT\Desktop\code\working\HRM\static\uploads\mau\hopdong\nt1\duoi_o2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DTD\Code\HRM\static\uploads\mau\hopdong\nt1\duoi_o2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DDE34C-0918-418B-AF43-25CC33EBB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D196953-FD52-47BC-8AE1-FD4AE9A38CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MẪU IN HỢP ĐỒNG LAO ĐỘNG" sheetId="2" r:id="rId1"/>
@@ -409,14 +409,14 @@
     <t xml:space="preserve">Số CCCD: </t>
   </si>
   <si>
-    <t>Địa chỉ: TDP 7 - Thuỷ Đường - Thuỷ Nguyên - Hải Phòng
+    <t>- Địa điểm làm việc: + Tổ dân phố 7, Phường Thủy Nguyên, TP Hải Phòng</t>
+  </si>
+  <si>
+    <t>Tổ dân phố 7, Phường Thủy Nguyên, TP Hải Phòng</t>
+  </si>
+  <si>
+    <t>Địa chỉ: TDP 7  - Thuỷ Nguyên - Hải Phòng
 ĐT: 02253.642.408</t>
-  </si>
-  <si>
-    <t>Tổ dân phố 7, Phường Thủy Đường, TP Thủy Nguyên, TP Hải Phòng</t>
-  </si>
-  <si>
-    <t>- Địa điểm làm việc: + Tổ dân phố 7, Phường Thủy Đường, TP Thủy Nguyên, TP Hải Phòng</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:X111"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="4" customWidth="1"/>
     <col min="9" max="10" width="8" customWidth="1"/>
@@ -1077,7 +1077,7 @@
     <col min="13" max="24" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1107,13 +1107,13 @@
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
     </row>
-    <row r="2" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -1137,7 +1137,7 @@
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
     </row>
-    <row r="3" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1167,7 +1167,7 @@
       <c r="W3" s="9"/>
       <c r="X3" s="9"/>
     </row>
-    <row r="4" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1197,7 +1197,7 @@
       <c r="W4" s="10"/>
       <c r="X4" s="10"/>
     </row>
-    <row r="5" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1223,7 +1223,7 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>6</v>
       </c>
@@ -1251,7 +1251,7 @@
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -1279,7 +1279,7 @@
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
     </row>
-    <row r="8" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1305,7 +1305,7 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="13" t="s">
         <v>8</v>
@@ -1333,7 +1333,7 @@
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="14" t="s">
         <v>9</v>
@@ -1367,7 +1367,7 @@
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
     </row>
-    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="14" t="s">
         <v>13</v>
@@ -1401,7 +1401,7 @@
       <c r="W11" s="14"/>
       <c r="X11" s="14"/>
     </row>
-    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="14" t="s">
         <v>17</v>
@@ -1431,7 +1431,7 @@
       <c r="W12" s="14"/>
       <c r="X12" s="14"/>
     </row>
-    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="14" t="s">
         <v>19</v>
@@ -1469,7 +1469,7 @@
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
     </row>
-    <row r="14" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="14" t="s">
         <v>25</v>
@@ -1499,7 +1499,7 @@
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
     </row>
-    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="14" t="s">
         <v>26</v>
@@ -1529,7 +1529,7 @@
       <c r="W15" s="14"/>
       <c r="X15" s="14"/>
     </row>
-    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="14" t="s">
         <v>27</v>
@@ -1563,7 +1563,7 @@
       <c r="W16" s="15"/>
       <c r="X16" s="15"/>
     </row>
-    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="13" t="s">
         <v>31</v>
@@ -1591,7 +1591,7 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="14" t="s">
         <v>9</v>
@@ -1625,7 +1625,7 @@
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
     </row>
-    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="14" t="s">
         <v>15</v>
@@ -1659,7 +1659,7 @@
       <c r="W19" s="14"/>
       <c r="X19" s="14"/>
     </row>
-    <row r="20" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="14" t="s">
         <v>17</v>
@@ -1689,7 +1689,7 @@
       <c r="W20" s="14"/>
       <c r="X20" s="14"/>
     </row>
-    <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="9" t="s">
         <v>128</v>
@@ -1727,7 +1727,7 @@
       <c r="W21" s="14"/>
       <c r="X21" s="14"/>
     </row>
-    <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="14" t="s">
         <v>27</v>
@@ -1755,7 +1755,7 @@
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="15" t="s">
         <v>39</v>
@@ -1783,7 +1783,7 @@
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
     </row>
-    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="13" t="s">
         <v>40</v>
@@ -1811,7 +1811,7 @@
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
     </row>
-    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="14" t="s">
         <v>41</v>
@@ -1841,7 +1841,7 @@
       <c r="W25" s="14"/>
       <c r="X25" s="14"/>
     </row>
-    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="14" t="s">
         <v>43</v>
@@ -1869,7 +1869,7 @@
       <c r="W26" s="14"/>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="14" t="s">
         <v>44</v>
@@ -1897,7 +1897,7 @@
       <c r="W27" s="14"/>
       <c r="X27" s="14"/>
     </row>
-    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="14" t="s">
         <v>45</v>
@@ -1925,7 +1925,7 @@
       <c r="W28" s="14"/>
       <c r="X28" s="14"/>
     </row>
-    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="14" t="s">
         <v>46</v>
@@ -1953,10 +1953,10 @@
       <c r="W29" s="14"/>
       <c r="X29" s="14"/>
     </row>
-    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -1981,7 +1981,7 @@
       <c r="W30" s="14"/>
       <c r="X30" s="14"/>
     </row>
-    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2009,7 +2009,7 @@
       <c r="W31" s="14"/>
       <c r="X31" s="14"/>
     </row>
-    <row r="32" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="14" t="s">
         <v>48</v>
@@ -2039,7 +2039,7 @@
       <c r="W32" s="18"/>
       <c r="X32" s="18"/>
     </row>
-    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="14" t="s">
         <v>50</v>
@@ -2069,7 +2069,7 @@
       <c r="W33" s="14"/>
       <c r="X33" s="14"/>
     </row>
-    <row r="34" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="14" t="s">
         <v>52</v>
@@ -2097,7 +2097,7 @@
       <c r="W34" s="14"/>
       <c r="X34" s="14"/>
     </row>
-    <row r="35" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="13" t="s">
         <v>53</v>
@@ -2125,7 +2125,7 @@
       <c r="W35" s="13"/>
       <c r="X35" s="13"/>
     </row>
-    <row r="36" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="14" t="s">
         <v>54</v>
@@ -2153,7 +2153,7 @@
       <c r="W36" s="14"/>
       <c r="X36" s="14"/>
     </row>
-    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="14" t="s">
         <v>55</v>
@@ -2181,7 +2181,7 @@
       <c r="W37" s="14"/>
       <c r="X37" s="14"/>
     </row>
-    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="14" t="s">
         <v>56</v>
@@ -2209,7 +2209,7 @@
       <c r="W38" s="14"/>
       <c r="X38" s="14"/>
     </row>
-    <row r="39" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="14" t="s">
         <v>57</v>
@@ -2237,7 +2237,7 @@
       <c r="W39" s="14"/>
       <c r="X39" s="14"/>
     </row>
-    <row r="40" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2263,7 +2263,7 @@
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
     </row>
-    <row r="41" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="13" t="s">
         <v>58</v>
@@ -2291,7 +2291,7 @@
       <c r="W41" s="13"/>
       <c r="X41" s="13"/>
     </row>
-    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="19" t="s">
         <v>59</v>
@@ -2319,7 +2319,7 @@
       <c r="W42" s="19"/>
       <c r="X42" s="19"/>
     </row>
-    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="13" t="s">
         <v>60</v>
@@ -2349,7 +2349,7 @@
       <c r="W43" s="18"/>
       <c r="X43" s="18"/>
     </row>
-    <row r="44" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="20" t="s">
         <v>62</v>
@@ -2377,7 +2377,7 @@
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
     </row>
-    <row r="45" spans="1:24" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2403,7 +2403,7 @@
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
     </row>
-    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="13" t="s">
         <v>63</v>
@@ -2433,7 +2433,7 @@
       <c r="W46" s="14"/>
       <c r="X46" s="14"/>
     </row>
-    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="14" t="s">
         <v>65</v>
@@ -2461,7 +2461,7 @@
       <c r="W47" s="14"/>
       <c r="X47" s="14"/>
     </row>
-    <row r="48" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="14" t="s">
         <v>66</v>
@@ -2489,7 +2489,7 @@
       <c r="W48" s="14"/>
       <c r="X48" s="14"/>
     </row>
-    <row r="49" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="13" t="s">
         <v>67</v>
@@ -2517,7 +2517,7 @@
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
     </row>
-    <row r="50" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="13" t="s">
         <v>68</v>
@@ -2547,7 +2547,7 @@
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
     </row>
-    <row r="51" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="14" t="s">
         <v>70</v>
@@ -2575,7 +2575,7 @@
       <c r="W51" s="14"/>
       <c r="X51" s="2"/>
     </row>
-    <row r="52" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="13" t="s">
         <v>71</v>
@@ -2603,7 +2603,7 @@
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
     </row>
-    <row r="53" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="14" t="s">
         <v>72</v>
@@ -2631,7 +2631,7 @@
       <c r="W53" s="14"/>
       <c r="X53" s="14"/>
     </row>
-    <row r="54" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="14" t="s">
         <v>73</v>
@@ -2659,7 +2659,7 @@
       <c r="W54" s="14"/>
       <c r="X54" s="14"/>
     </row>
-    <row r="55" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="13" t="s">
         <v>74</v>
@@ -2687,7 +2687,7 @@
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
     </row>
-    <row r="56" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="14" t="s">
         <v>75</v>
@@ -2715,7 +2715,7 @@
       <c r="W56" s="14"/>
       <c r="X56" s="14"/>
     </row>
-    <row r="57" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="14" t="s">
         <v>76</v>
@@ -2743,7 +2743,7 @@
       <c r="W57" s="14"/>
       <c r="X57" s="14"/>
     </row>
-    <row r="58" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="14" t="s">
         <v>77</v>
@@ -2771,7 +2771,7 @@
       <c r="W58" s="14"/>
       <c r="X58" s="14"/>
     </row>
-    <row r="59" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="13" t="s">
         <v>78</v>
@@ -2799,7 +2799,7 @@
       <c r="W59" s="13"/>
       <c r="X59" s="13"/>
     </row>
-    <row r="60" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="14" t="s">
         <v>79</v>
@@ -2827,7 +2827,7 @@
       <c r="W60" s="14"/>
       <c r="X60" s="14"/>
     </row>
-    <row r="61" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="13" t="s">
         <v>80</v>
@@ -2855,7 +2855,7 @@
       <c r="W61" s="13"/>
       <c r="X61" s="13"/>
     </row>
-    <row r="62" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="13" t="s">
         <v>81</v>
@@ -2883,7 +2883,7 @@
       <c r="W62" s="13"/>
       <c r="X62" s="13"/>
     </row>
-    <row r="63" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="14" t="s">
         <v>82</v>
@@ -2911,7 +2911,7 @@
       <c r="W63" s="14"/>
       <c r="X63" s="14"/>
     </row>
-    <row r="64" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="14" t="s">
         <v>83</v>
@@ -2939,7 +2939,7 @@
       <c r="W64" s="14"/>
       <c r="X64" s="14"/>
     </row>
-    <row r="65" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="14" t="s">
         <v>84</v>
@@ -2967,7 +2967,7 @@
       <c r="W65" s="14"/>
       <c r="X65" s="14"/>
     </row>
-    <row r="66" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="13" t="s">
         <v>127</v>
@@ -2995,7 +2995,7 @@
       <c r="W66" s="13"/>
       <c r="X66" s="13"/>
     </row>
-    <row r="67" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="13" t="s">
         <v>85</v>
@@ -3023,7 +3023,7 @@
       <c r="W67" s="13"/>
       <c r="X67" s="13"/>
     </row>
-    <row r="68" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="14" t="s">
         <v>86</v>
@@ -3051,7 +3051,7 @@
       <c r="W68" s="14"/>
       <c r="X68" s="14"/>
     </row>
-    <row r="69" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="14" t="s">
         <v>87</v>
@@ -3079,7 +3079,7 @@
       <c r="W69" s="14"/>
       <c r="X69" s="14"/>
     </row>
-    <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="14" t="s">
         <v>88</v>
@@ -3107,7 +3107,7 @@
       <c r="W70" s="14"/>
       <c r="X70" s="14"/>
     </row>
-    <row r="71" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="14" t="s">
         <v>89</v>
@@ -3135,7 +3135,7 @@
       <c r="W71" s="14"/>
       <c r="X71" s="2"/>
     </row>
-    <row r="72" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="14" t="s">
         <v>90</v>
@@ -3163,7 +3163,7 @@
       <c r="W72" s="14"/>
       <c r="X72" s="14"/>
     </row>
-    <row r="73" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="14" t="s">
         <v>91</v>
@@ -3191,7 +3191,7 @@
       <c r="W73" s="14"/>
       <c r="X73" s="14"/>
     </row>
-    <row r="74" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="14" t="s">
         <v>92</v>
@@ -3219,7 +3219,7 @@
       <c r="W74" s="14"/>
       <c r="X74" s="14"/>
     </row>
-    <row r="75" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="19" t="s">
         <v>93</v>
@@ -3247,7 +3247,7 @@
       <c r="W75" s="19"/>
       <c r="X75" s="19"/>
     </row>
-    <row r="76" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="14" t="s">
         <v>94</v>
@@ -3275,7 +3275,7 @@
       <c r="W76" s="14"/>
       <c r="X76" s="14"/>
     </row>
-    <row r="77" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="14" t="s">
         <v>95</v>
@@ -3303,7 +3303,7 @@
       <c r="W77" s="14"/>
       <c r="X77" s="14"/>
     </row>
-    <row r="78" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="14" t="s">
         <v>96</v>
@@ -3331,7 +3331,7 @@
       <c r="W78" s="14"/>
       <c r="X78" s="14"/>
     </row>
-    <row r="79" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="14" t="s">
         <v>97</v>
@@ -3359,7 +3359,7 @@
       <c r="W79" s="14"/>
       <c r="X79" s="14"/>
     </row>
-    <row r="80" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="14" t="s">
         <v>98</v>
@@ -3387,7 +3387,7 @@
       <c r="W80" s="14"/>
       <c r="X80" s="14"/>
     </row>
-    <row r="81" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="14" t="s">
         <v>99</v>
@@ -3415,7 +3415,7 @@
       <c r="W81" s="14"/>
       <c r="X81" s="14"/>
     </row>
-    <row r="82" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="14" t="s">
         <v>100</v>
@@ -3443,7 +3443,7 @@
       <c r="W82" s="14"/>
       <c r="X82" s="14"/>
     </row>
-    <row r="83" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="14" t="s">
         <v>101</v>
@@ -3471,7 +3471,7 @@
       <c r="W83" s="14"/>
       <c r="X83" s="14"/>
     </row>
-    <row r="84" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="14" t="s">
         <v>102</v>
@@ -3499,7 +3499,7 @@
       <c r="W84" s="14"/>
       <c r="X84" s="14"/>
     </row>
-    <row r="85" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="14" t="s">
         <v>103</v>
@@ -3527,7 +3527,7 @@
       <c r="W85" s="14"/>
       <c r="X85" s="14"/>
     </row>
-    <row r="86" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="14" t="s">
         <v>104</v>
@@ -3555,7 +3555,7 @@
       <c r="W86" s="14"/>
       <c r="X86" s="14"/>
     </row>
-    <row r="87" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="13" t="s">
         <v>105</v>
@@ -3583,7 +3583,7 @@
       <c r="W87" s="13"/>
       <c r="X87" s="13"/>
     </row>
-    <row r="88" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="13" t="s">
         <v>106</v>
@@ -3611,7 +3611,7 @@
       <c r="W88" s="13"/>
       <c r="X88" s="13"/>
     </row>
-    <row r="89" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="14" t="s">
         <v>107</v>
@@ -3639,7 +3639,7 @@
       <c r="W89" s="14"/>
       <c r="X89" s="14"/>
     </row>
-    <row r="90" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="14" t="s">
         <v>108</v>
@@ -3667,7 +3667,7 @@
       <c r="W90" s="14"/>
       <c r="X90" s="14"/>
     </row>
-    <row r="91" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="14" t="s">
         <v>109</v>
@@ -3695,7 +3695,7 @@
       <c r="W91" s="14"/>
       <c r="X91" s="14"/>
     </row>
-    <row r="92" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="14" t="s">
         <v>110</v>
@@ -3723,7 +3723,7 @@
       <c r="W92" s="14"/>
       <c r="X92" s="14"/>
     </row>
-    <row r="93" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="13" t="s">
         <v>111</v>
@@ -3751,7 +3751,7 @@
       <c r="W93" s="13"/>
       <c r="X93" s="13"/>
     </row>
-    <row r="94" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="14" t="s">
         <v>112</v>
@@ -3779,7 +3779,7 @@
       <c r="W94" s="14"/>
       <c r="X94" s="14"/>
     </row>
-    <row r="95" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="14" t="s">
         <v>113</v>
@@ -3807,7 +3807,7 @@
       <c r="W95" s="14"/>
       <c r="X95" s="14"/>
     </row>
-    <row r="96" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="14" t="s">
         <v>114</v>
@@ -3835,7 +3835,7 @@
       <c r="W96" s="14"/>
       <c r="X96" s="14"/>
     </row>
-    <row r="97" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="13" t="s">
         <v>115</v>
@@ -3863,7 +3863,7 @@
       <c r="W97" s="13"/>
       <c r="X97" s="13"/>
     </row>
-    <row r="98" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="14" t="s">
         <v>116</v>
@@ -3891,7 +3891,7 @@
       <c r="W98" s="14"/>
       <c r="X98" s="14"/>
     </row>
-    <row r="99" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="14" t="s">
         <v>117</v>
@@ -3919,7 +3919,7 @@
       <c r="W99" s="14"/>
       <c r="X99" s="14"/>
     </row>
-    <row r="100" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="14" t="s">
         <v>118</v>
@@ -3947,7 +3947,7 @@
       <c r="W100" s="14"/>
       <c r="X100" s="14"/>
     </row>
-    <row r="101" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="14" t="s">
         <v>119</v>
@@ -3975,7 +3975,7 @@
       <c r="W101" s="14"/>
       <c r="X101" s="14"/>
     </row>
-    <row r="102" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="21" t="s">
         <v>120</v>
@@ -4005,7 +4005,7 @@
       <c r="W102" s="21"/>
       <c r="X102" s="21"/>
     </row>
-    <row r="103" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="10" t="s">
         <v>122</v>
@@ -4033,7 +4033,7 @@
       <c r="W103" s="10"/>
       <c r="X103" s="10"/>
     </row>
-    <row r="104" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4059,7 +4059,7 @@
       <c r="W104" s="2"/>
       <c r="X104" s="2"/>
     </row>
-    <row r="105" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4085,7 +4085,7 @@
       <c r="W105" s="2"/>
       <c r="X105" s="2"/>
     </row>
-    <row r="106" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4111,7 +4111,7 @@
       <c r="W106" s="2"/>
       <c r="X106" s="2"/>
     </row>
-    <row r="107" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4137,7 +4137,7 @@
       <c r="W107" s="2"/>
       <c r="X107" s="2"/>
     </row>
-    <row r="108" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4167,7 +4167,7 @@
       <c r="W108" s="14"/>
       <c r="X108" s="14"/>
     </row>
-    <row r="109" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4195,7 +4195,7 @@
       <c r="W109" s="14"/>
       <c r="X109" s="2"/>
     </row>
-    <row r="110" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4225,7 +4225,7 @@
       <c r="W110" s="2"/>
       <c r="X110" s="2"/>
     </row>
-    <row r="111" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
